--- a/Graph/Others/WT-T2-TiTa_outward_filtered.xlsx
+++ b/Graph/Others/WT-T2-TiTa_outward_filtered.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agrawal-admin\Desktop\Landing\Graph\Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C5D146-0D04-4671-8BFF-5DD395E51F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D541BFF-1E75-4C9E-A9FE-F53B50B6FD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="25">
   <si>
     <t>Fly#</t>
   </si>
@@ -680,8 +680,8 @@
       <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>24</v>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="F3" s="2">
         <v>61</v>
@@ -769,8 +769,8 @@
       <c r="L4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>24</v>
+      <c r="M4" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>24</v>
@@ -866,8 +866,8 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>41</v>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>21</v>
@@ -931,8 +931,8 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>132</v>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>23</v>
@@ -1197,14 +1197,14 @@
       <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>24</v>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>21</v>
@@ -1354,8 +1354,8 @@
       <c r="L13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M13" s="7" t="s">
-        <v>24</v>
+      <c r="M13" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>21</v>
@@ -1561,8 +1561,8 @@
       <c r="P16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Q16" s="7" t="s">
-        <v>24</v>
+      <c r="Q16" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="R16" s="7" t="s">
         <v>24</v>
